--- a/skills/proto/assets/Adventure_template/Adventure_template.xlsx
+++ b/skills/proto/assets/Adventure_template/Adventure_template.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="2" max="2"/>
@@ -1525,114 +1525,344 @@
       </c>
       <c r="L5" s="45" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="45" t="n"/>
-      <c r="B6" s="46" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E7" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F7" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G7" s="47" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H7" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I7" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" s="47" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n"/>
+      <c r="L7" s="47" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="47" t="n"/>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>classname</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F8" s="47" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G8" s="47" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="H8" s="47" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="I8" s="47" t="inlineStr">
+        <is>
+          <t>meta_info</t>
+        </is>
+      </c>
+      <c r="J8" s="47" t="inlineStr">
+        <is>
+          <t>rand_reward</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="n"/>
+      <c r="L8" s="47" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="n"/>
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>/mystery_box/Adventure/Adventure_3_Sport_Box_2.proto.js</t>
         </is>
       </c>
-      <c r="C6" s="45" t="inlineStr">
+      <c r="C9" s="45" t="inlineStr">
         <is>
           <t>/mystery_box/Adventure/Adventure_3_Sport_Box_2.proto.js</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D9" s="45" t="inlineStr">
         <is>
           <t>Adventure_3_Sport_Box_2</t>
         </is>
       </c>
-      <c r="E6" s="45" t="inlineStr">
+      <c r="E9" s="45" t="inlineStr">
         <is>
           <t>Теннисная коробка с подарками</t>
         </is>
       </c>
-      <c r="F6" s="45" t="inlineStr">
+      <c r="F9" s="45" t="inlineStr">
         <is>
           <t>Содержит: 2 бустера для мгновенной уборки мусора со всех горшков в локации, 15 оживителей, 15 ускорителей, 20 жетонов</t>
         </is>
       </c>
-      <c r="G6" s="45" t="n">
+      <c r="G9" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="45" t="inlineStr">
+      <c r="H9" s="45" t="inlineStr">
         <is>
           <t>money_alt</t>
         </is>
       </c>
-      <c r="I6" s="45" t="inlineStr">
+      <c r="I9" s="45" t="inlineStr">
         <is>
           <t>plan=first</t>
         </is>
       </c>
-      <c r="J6" s="45" t="inlineStr">
+      <c r="J9" s="45" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="K6" s="45" t="inlineStr">
+      <c r="K9" s="45" t="inlineStr">
         <is>
           <t>[{"asset":"Stuff_Booster_CleanPot","amount":2},{"asset":"RecoverPlantBooster","amount":15},{"asset":"AccelerationPlantBooster","amount":15},{"asset":"AccelerateCraftingBooster","amount":20},{"asset":"Shop_of_miracles_GR_1","amount":30}]</t>
         </is>
       </c>
-      <c r="L6" s="45" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="45" t="n"/>
-      <c r="B7" s="46" t="inlineStr">
+      <c r="L9" s="45" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F11" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G11" s="47" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H11" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I11" s="47" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" s="47" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="n"/>
+      <c r="L11" s="47" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="47" t="n"/>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>classname</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F12" s="47" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G12" s="47" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="H12" s="47" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="I12" s="47" t="inlineStr">
+        <is>
+          <t>meta_info</t>
+        </is>
+      </c>
+      <c r="J12" s="47" t="inlineStr">
+        <is>
+          <t>rand_reward</t>
+        </is>
+      </c>
+      <c r="K12" s="48" t="n"/>
+      <c r="L12" s="47" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="n"/>
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>/mystery_box/Adventure/Adventure_3_Sport_Box_3.proto.js</t>
         </is>
       </c>
-      <c r="C7" s="45" t="inlineStr">
+      <c r="C13" s="45" t="inlineStr">
         <is>
           <t>/mystery_box/Adventure/Adventure_3_Sport_Box_3.proto.js</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D13" s="45" t="inlineStr">
         <is>
           <t>Adventure_3_Sport_Box_3</t>
         </is>
       </c>
-      <c r="E7" s="45" t="inlineStr">
+      <c r="E13" s="45" t="inlineStr">
         <is>
           <t>Баскетбольная коробка с подарками</t>
         </is>
       </c>
-      <c r="F7" s="45" t="inlineStr">
+      <c r="F13" s="45" t="inlineStr">
         <is>
           <t>Коробка содержит: 4 бустеров для мгновенной уборки мусора со всех горшков в локации, 20 оживителей, 20 ускорителей, 30 жетонов</t>
         </is>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G13" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="45" t="inlineStr">
+      <c r="H13" s="45" t="inlineStr">
         <is>
           <t>money_alt</t>
         </is>
       </c>
-      <c r="I7" s="45" t="inlineStr">
+      <c r="I13" s="45" t="inlineStr">
         <is>
           <t>plan=first</t>
         </is>
       </c>
-      <c r="J7" s="45" t="inlineStr">
+      <c r="J13" s="45" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="K7" s="45" t="inlineStr">
+      <c r="K13" s="45" t="inlineStr">
         <is>
           <t>[{"asset":"Stuff_Booster_CleanPot","amount":4},{"asset":"RecoverPlantBooster","amount":20},{"asset":"AccelerationPlantBooster","amount":20},{"asset":"AccelerateCraftingBooster","amount":30},{"asset":"Shop_of_miracles_GR_1","amount":50}]</t>
         </is>
       </c>
-      <c r="L7" s="45" t="n"/>
+      <c r="L13" s="45" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3072,9 +3302,9 @@
     <col width="63.5703125" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="17.28515625" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="92.7109375" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="21.42578125" customWidth="1" min="12" max="12"/>
@@ -3177,8 +3407,16 @@
           <t>int</t>
         </is>
       </c>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="6" t="n"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="J3" s="6" t="n"/>
       <c r="K3" s="6" t="n"/>
       <c r="L3" s="6" t="n"/>
@@ -3225,8 +3463,16 @@
           <t>id</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.identifier</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
@@ -3290,8 +3536,16 @@
       <c r="B6" s="14" t="n"/>
       <c r="C6" s="14" t="n"/>
       <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="n"/>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Adventure_GR_3</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Adventure_GR_3</t>
+        </is>
+      </c>
       <c r="G6" s="14" t="n"/>
       <c r="H6" s="14" t="n"/>
       <c r="I6" s="14" t="n"/>
@@ -3627,7 +3881,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="J18" s="6" t="n"/>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="6" t="n"/>
       <c r="M18" s="6" t="n"/>
@@ -3679,7 +3937,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="J19" s="6" t="n"/>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="6" t="n"/>
       <c r="M19" s="6" t="n"/>
@@ -3913,7 +4175,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="H27" s="6" t="n"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
@@ -3961,7 +4227,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="H28" s="6" t="n"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
@@ -4209,7 +4479,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="J36" s="6" t="n"/>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="6" t="n"/>
       <c r="M36" s="6" t="n"/>
@@ -4265,7 +4539,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="J37" s="6" t="n"/>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="K37" s="6" t="n"/>
       <c r="L37" s="6" t="n"/>
       <c r="M37" s="6" t="n"/>
@@ -4514,7 +4792,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="H45" s="6" t="n"/>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I45" s="6" t="n"/>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
@@ -4563,7 +4845,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="H46" s="6" t="n"/>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
@@ -4813,7 +5099,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="J54" s="6" t="n"/>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="K54" s="6" t="n"/>
       <c r="L54" s="6" t="n"/>
       <c r="M54" s="6" t="n"/>
@@ -4869,7 +5159,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="J55" s="6" t="n"/>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="K55" s="6" t="n"/>
       <c r="L55" s="6" t="n"/>
       <c r="M55" s="6" t="n"/>
@@ -5117,7 +5411,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="H63" s="6" t="n"/>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I63" s="6" t="n"/>
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="6" t="n"/>
@@ -5166,7 +5464,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="H64" s="6" t="n"/>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I64" s="6" t="n"/>
       <c r="J64" s="6" t="n"/>
       <c r="K64" s="6" t="n"/>
@@ -5405,8 +5707,16 @@
           <t>int</t>
         </is>
       </c>
-      <c r="G72" s="6" t="n"/>
-      <c r="H72" s="6" t="n"/>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I72" s="6" t="n"/>
       <c r="J72" s="6" t="n"/>
       <c r="K72" s="6" t="n"/>
@@ -5450,8 +5760,16 @@
           <t>id</t>
         </is>
       </c>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="6" t="n"/>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.identifier</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I73" s="6" t="n"/>
       <c r="J73" s="6" t="n"/>
       <c r="K73" s="6" t="n"/>
@@ -5665,8 +5983,16 @@
           <t>int</t>
         </is>
       </c>
-      <c r="G80" s="6" t="n"/>
-      <c r="H80" s="6" t="n"/>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I80" s="6" t="n"/>
       <c r="J80" s="6" t="n"/>
       <c r="K80" s="6" t="n"/>
@@ -5709,8 +6035,16 @@
           <t>id</t>
         </is>
       </c>
-      <c r="G81" s="6" t="n"/>
-      <c r="H81" s="6" t="n"/>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.identifier</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I81" s="6" t="n"/>
       <c r="J81" s="6" t="n"/>
       <c r="K81" s="6" t="n"/>
@@ -9338,7 +9672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9594,7 +9928,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>AdventureConfirmWindow</t>
+          <t>FairyTaleConfirmWindow</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -9626,7 +9960,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>AdventureQuestCompleteWindow</t>
+          <t>FairyTaleQuestCompleteWindow</t>
         </is>
       </c>
       <c r="J6" s="14" t="n"/>
@@ -9659,7 +9993,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>AdventureQuestProgressWindow</t>
+          <t>FairyTaleQuestProgressWindow</t>
         </is>
       </c>
       <c r="J7" s="14" t="n"/>
@@ -9692,7 +10026,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>{"view_classname":"AdventureQuestRuleWindow","title":"Правила","description":"Спортивные соревнования - это особое событие, в котором требуется выполнять задания за ограниченное время. Кроме выполнения, любое задание можно сбросить, тогда оно исчезнет. В обоих случаях нужно подождать 30 минут, чтобы получить новое задание. А если выполнить все 3 задания, то мгновенно появятся 3 новых! Выполняя задания, ты получаешь Факелы, а набрав нужное количество, получишь награду и будешь двигаться к следующей. Среди наград - спортивный декор, волшебство, волшебная жаба, чудесные спортивные горшочки, а главный приз - новый уникальный крохонька! Не теряйте времени! У вас есть всего 2 дня чтобы получить все награды, удачи!"}</t>
+          <t>{"view_classname":"FairyTaleQuestRuleWindow","title":"Правила","description":"Спортивные соревнования - это особое событие, в котором требуется выполнять задания за ограниченное время. Кроме выполнения, любое задание можно сбросить, тогда оно исчезнет. В обоих случаях нужно подождать 30 минут, чтобы получить новое задание. А если выполнить все 3 задания, то мгновенно появятся 3 новых! Выполняя задания, ты получаешь Факелы, а набрав нужное количество, получишь награду и будешь двигаться к следующей. Среди наград - спортивный декор, волшебство, волшебная жаба, чудесные спортивные горшочки, а главный приз - новый уникальный крохонька! Не теряйте времени! У вас есть всего 2 дня чтобы получить все награды, удачи!"}</t>
         </is>
       </c>
       <c r="J8" s="14" t="n"/>
@@ -9725,7 +10059,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>{"view_classname":"AdventureQuestWindow","quest_task_item":"AdventureQuestTaskItem"}</t>
+          <t>{"view_classname":"FairyTaleQuestWindow","quest_task_item":"FairyTaleQuestTaskItem"}</t>
         </is>
       </c>
       <c r="J9" s="14" t="n"/>
@@ -10005,86 +10339,39 @@
       <c r="AC15" s="14" t="n"/>
       <c r="AD15" s="14" t="n"/>
     </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="14" t="n"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_quest_task_2_restarter.proto.js</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_quest_task_2_restarter.proto.js</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Adventure_3_Sport_9_quest_task_2_restarter</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Adventure_3_Sport_9</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Adventure_3_Sport_9</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-      <c r="R16" s="14" t="n"/>
-      <c r="S16" s="14" t="n"/>
-      <c r="T16" s="14" t="n"/>
-      <c r="U16" s="14" t="n"/>
-      <c r="V16" s="14" t="n"/>
-      <c r="W16" s="14" t="n"/>
-      <c r="X16" s="14" t="n"/>
-      <c r="Y16" s="14" t="n"/>
-      <c r="Z16" s="14" t="n"/>
-      <c r="AA16" s="14" t="n"/>
-      <c r="AB16" s="14" t="n"/>
-      <c r="AC16" s="14" t="n"/>
-      <c r="AD16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="14" t="n"/>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>sl</t>
+        </is>
+      </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_quest_task_3_restarter.proto.js</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_quest_task_3_restarter.proto.js</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Adventure_3_Sport_9_quest_task_3_restarter</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Adventure_3_Sport_9</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Adventure_3_Sport_9</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="n"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
@@ -10093,7 +10380,6 @@
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
       <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
       <c r="Q17" s="14" t="n"/>
       <c r="R17" s="14" t="n"/>
       <c r="S17" s="14" t="n"/>
@@ -10111,21 +10397,44 @@
     </row>
     <row r="18">
       <c r="A18" s="14" t="n"/>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="14" t="n"/>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="14" t="n"/>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>find</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
       <c r="Q18" s="14" t="n"/>
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="n"/>
@@ -10141,27 +10450,43 @@
       <c r="AC18" s="14" t="n"/>
       <c r="AD18" s="14" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="14" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>tech - flat rows</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="14" t="n"/>
-      <c r="I19" s="14" t="n"/>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="14" t="n"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="14" t="n"/>
-      <c r="N19" s="14" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_quest_task_2_restarter.proto.js</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_quest_task_2_restarter.proto.js</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Adventure_3_Sport_9_quest_task_2_restarter</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Adventure_3_Sport_9</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Adventure_3_Sport_9</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
       <c r="Q19" s="14" t="n"/>
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="n"/>
@@ -10177,91 +10502,37 @@
       <c r="AC19" s="14" t="n"/>
       <c r="AD19" s="14" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>sl</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E20" s="36" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>replace</t>
         </is>
       </c>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>int</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n"/>
-      <c r="N20" s="6" t="n"/>
-      <c r="P20" s="14" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-      <c r="R20" s="14" t="n"/>
-      <c r="S20" s="14" t="n"/>
-      <c r="T20" s="14" t="n"/>
-      <c r="U20" s="14" t="n"/>
-      <c r="V20" s="14" t="n"/>
-      <c r="W20" s="14" t="n"/>
-      <c r="X20" s="14" t="n"/>
-      <c r="Y20" s="14" t="n"/>
-      <c r="Z20" s="14" t="n"/>
-      <c r="AA20" s="14" t="n"/>
-      <c r="AB20" s="14" t="n"/>
-      <c r="AC20" s="14" t="n"/>
-      <c r="AD20" s="14" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="n"/>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>identifier</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>find</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>replace</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
         </is>
       </c>
       <c r="H21" s="6" t="n"/>
@@ -10271,7 +10542,7 @@
       <c r="L21" s="6" t="n"/>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="P21" s="14" t="n"/>
+      <c r="O21" s="6" t="n"/>
       <c r="Q21" s="14" t="n"/>
       <c r="R21" s="14" t="n"/>
       <c r="S21" s="14" t="n"/>
@@ -10287,34 +10558,38 @@
       <c r="AC21" s="14" t="n"/>
       <c r="AD21" s="14" t="n"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22">
       <c r="A22" s="14" t="n"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_tech.proto.js</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_tech.proto.js</t>
+          <t>output</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Adventure_3_Sport_9_tech</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Adventure_3_Sport_9</t>
+          <t>find</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Adventure_3_Sport_9</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
@@ -10322,7 +10597,7 @@
       <c r="L22" s="6" t="n"/>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="P22" s="14" t="n"/>
+      <c r="O22" s="6" t="n"/>
       <c r="Q22" s="14" t="n"/>
       <c r="R22" s="14" t="n"/>
       <c r="S22" s="14" t="n"/>
@@ -10338,12 +10613,295 @@
       <c r="AC22" s="14" t="n"/>
       <c r="AD22" s="14" t="n"/>
     </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_quest_task_3_restarter.proto.js</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_quest_task_3_restarter.proto.js</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Adventure_3_Sport_9_quest_task_3_restarter</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Adventure_3_Sport_9</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Adventure_3_Sport_9</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="14" t="n"/>
+      <c r="R23" s="14" t="n"/>
+      <c r="S23" s="14" t="n"/>
+      <c r="T23" s="14" t="n"/>
+      <c r="U23" s="14" t="n"/>
+      <c r="V23" s="14" t="n"/>
+      <c r="W23" s="14" t="n"/>
+      <c r="X23" s="14" t="n"/>
+      <c r="Y23" s="14" t="n"/>
+      <c r="Z23" s="14" t="n"/>
+      <c r="AA23" s="14" t="n"/>
+      <c r="AB23" s="14" t="n"/>
+      <c r="AC23" s="14" t="n"/>
+      <c r="AD23" s="14" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="14" t="n"/>
+      <c r="O24" s="14" t="n"/>
+      <c r="P24" s="14" t="n"/>
+      <c r="Q24" s="14" t="n"/>
+      <c r="R24" s="14" t="n"/>
+      <c r="S24" s="14" t="n"/>
+      <c r="T24" s="14" t="n"/>
+      <c r="U24" s="14" t="n"/>
+      <c r="V24" s="14" t="n"/>
+      <c r="W24" s="14" t="n"/>
+      <c r="X24" s="14" t="n"/>
+      <c r="Y24" s="14" t="n"/>
+      <c r="Z24" s="14" t="n"/>
+      <c r="AA24" s="14" t="n"/>
+      <c r="AB24" s="14" t="n"/>
+      <c r="AC24" s="14" t="n"/>
+      <c r="AD24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>tech - flat rows</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="14" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="14" t="n"/>
+      <c r="N25" s="14" t="n"/>
+      <c r="O25" s="14" t="n"/>
+      <c r="P25" s="14" t="n"/>
+      <c r="Q25" s="14" t="n"/>
+      <c r="R25" s="14" t="n"/>
+      <c r="S25" s="14" t="n"/>
+      <c r="T25" s="14" t="n"/>
+      <c r="U25" s="14" t="n"/>
+      <c r="V25" s="14" t="n"/>
+      <c r="W25" s="14" t="n"/>
+      <c r="X25" s="14" t="n"/>
+      <c r="Y25" s="14" t="n"/>
+      <c r="Z25" s="14" t="n"/>
+      <c r="AA25" s="14" t="n"/>
+      <c r="AB25" s="14" t="n"/>
+      <c r="AC25" s="14" t="n"/>
+      <c r="AD25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>sl</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E26" s="36" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="P26" s="14" t="n"/>
+      <c r="Q26" s="14" t="n"/>
+      <c r="R26" s="14" t="n"/>
+      <c r="S26" s="14" t="n"/>
+      <c r="T26" s="14" t="n"/>
+      <c r="U26" s="14" t="n"/>
+      <c r="V26" s="14" t="n"/>
+      <c r="W26" s="14" t="n"/>
+      <c r="X26" s="14" t="n"/>
+      <c r="Y26" s="14" t="n"/>
+      <c r="Z26" s="14" t="n"/>
+      <c r="AA26" s="14" t="n"/>
+      <c r="AB26" s="14" t="n"/>
+      <c r="AC26" s="14" t="n"/>
+      <c r="AD26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>find</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n"/>
+      <c r="P27" s="14" t="n"/>
+      <c r="Q27" s="14" t="n"/>
+      <c r="R27" s="14" t="n"/>
+      <c r="S27" s="14" t="n"/>
+      <c r="T27" s="14" t="n"/>
+      <c r="U27" s="14" t="n"/>
+      <c r="V27" s="14" t="n"/>
+      <c r="W27" s="14" t="n"/>
+      <c r="X27" s="14" t="n"/>
+      <c r="Y27" s="14" t="n"/>
+      <c r="Z27" s="14" t="n"/>
+      <c r="AA27" s="14" t="n"/>
+      <c r="AB27" s="14" t="n"/>
+      <c r="AC27" s="14" t="n"/>
+      <c r="AD27" s="14" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="14" t="n"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_tech.proto.js</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>/quest_group/marketing_action/Adventure/Adventure_3_Sport/Adventure_3_Sport_9/Adventure_3_Sport_9_tech.proto.js</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Adventure_3_Sport_9_tech</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Adventure_3_Sport_9</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Adventure_3_Sport_9</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="P28" s="14" t="n"/>
+      <c r="Q28" s="14" t="n"/>
+      <c r="R28" s="14" t="n"/>
+      <c r="S28" s="14" t="n"/>
+      <c r="T28" s="14" t="n"/>
+      <c r="U28" s="14" t="n"/>
+      <c r="V28" s="14" t="n"/>
+      <c r="W28" s="14" t="n"/>
+      <c r="X28" s="14" t="n"/>
+      <c r="Y28" s="14" t="n"/>
+      <c r="Z28" s="14" t="n"/>
+      <c r="AA28" s="14" t="n"/>
+      <c r="AB28" s="14" t="n"/>
+      <c r="AC28" s="14" t="n"/>
+      <c r="AD28" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10355,7 +10913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10365,6 +10923,8 @@
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10432,6 +10992,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n"/>
@@ -10470,6 +11040,16 @@
           <t>id</t>
         </is>
       </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.identifier</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="n"/>
@@ -10495,12 +11075,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>TrophyPet17_Sport_9</t>
+          <t>Pet17_Sport_9</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>TrophyPet17_Sport_9</t>
+          <t>Pet17_Sport_9</t>
         </is>
       </c>
       <c r="H5" s="6" t="n"/>
